--- a/DateBase/orders/Nha Thu_2026-7-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-4.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>099418105515100</v>
+        <v>099418105515105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,71 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>315_尤加利叶圆叶_Eucalyptus Populus_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F15" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16" t="str">
+        <v>334_狗尾草_puppy tail grass_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +643,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>099418105515105</v>
+        <v>0994181055151051520515102015</v>
       </c>
     </row>
   </sheetData>
